--- a/shared/ojb-resources-common/src/main/resources/ssp/Uniform_Commitment_Order_Reporting_Response/artifacts/service_model/information_model/IEPD/documentation/UniformCommitmentOrderReportingResponseMapping.xlsx
+++ b/shared/ojb-resources-common/src/main/resources/ssp/Uniform_Commitment_Order_Reporting_Response/artifacts/service_model/information_model/IEPD/documentation/UniformCommitmentOrderReportingResponseMapping.xlsx
@@ -5,12 +5,12 @@
   <workbookPr date1904="1" showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaeljacobson/Documents/SEARCH/Louisiana ICJIS/phase 4/Uniform_Commitment_Order_Reporting_Response/artifacts/service_model/information_model/IEPD/documentation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaeljacobson/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09119C0-A312-0F41-9C52-12A54B546E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E696F7-16C7-CD47-B3F9-26826A92ABA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58700" yWindow="2320" windowWidth="35820" windowHeight="15800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="65880" yWindow="4220" windowWidth="35820" windowHeight="15800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UCO Reporting Response" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>CLASS</t>
   </si>
@@ -88,6 +88,24 @@
   </si>
   <si>
     <t>Document Identifier</t>
+  </si>
+  <si>
+    <t>Parish Code</t>
+  </si>
+  <si>
+    <t>Parish Name</t>
+  </si>
+  <si>
+    <t>/uco-resp:UniformCommitmentOrderReportingResponse/nc:Document/ucoresp-ext:ParishCodeText</t>
+  </si>
+  <si>
+    <t>/uco-resp:UniformCommitmentOrderReportingResponse/nc:Document/ucoresp-ext:ParishCodeDescriptionText</t>
+  </si>
+  <si>
+    <t>ParishCode</t>
+  </si>
+  <si>
+    <t>ParishName</t>
   </si>
 </sst>
 </file>
@@ -2075,7 +2093,7 @@
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
     </row>
-    <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
@@ -2135,13 +2153,27 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
+      <c r="B9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
+      <c r="B10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
@@ -2176,7 +2208,6 @@
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
@@ -2191,7 +2222,6 @@
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
@@ -2201,7 +2231,6 @@
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
